--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137221693</v>
       </c>
       <c r="B3" t="n">
-        <v>87388</v>
+        <v>87401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>137221872</v>
       </c>
       <c r="B6" t="n">
-        <v>87563</v>
+        <v>87576</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>137221873</v>
       </c>
       <c r="B8" t="n">
-        <v>90841</v>
+        <v>90854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>137222914</v>
       </c>
       <c r="B9" t="n">
-        <v>90841</v>
+        <v>90854</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>137221700</v>
       </c>
       <c r="B14" t="n">
-        <v>91563</v>
+        <v>91576</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>137221671</v>
       </c>
       <c r="B15" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>137221853</v>
       </c>
       <c r="B16" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>137221857</v>
       </c>
       <c r="B17" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>137221874</v>
       </c>
       <c r="B18" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>137222844</v>
       </c>
       <c r="B19" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>137222846</v>
       </c>
       <c r="B20" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>137222850</v>
       </c>
       <c r="B21" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>137222857</v>
       </c>
       <c r="B22" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>137222908</v>
       </c>
       <c r="B23" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>137222909</v>
       </c>
       <c r="B24" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>137222912</v>
       </c>
       <c r="B25" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137221668</v>
       </c>
       <c r="B28" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>137221673</v>
       </c>
       <c r="B31" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>137221694</v>
       </c>
       <c r="B32" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>137221869</v>
       </c>
       <c r="B33" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>137221674</v>
       </c>
       <c r="B36" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>137221859</v>
       </c>
       <c r="B37" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>137221864</v>
       </c>
       <c r="B38" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>137221868</v>
       </c>
       <c r="B39" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>137222910</v>
       </c>
       <c r="B40" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>137221669</v>
       </c>
       <c r="B43" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>137221670</v>
       </c>
       <c r="B44" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>137221676</v>
       </c>
       <c r="B45" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>137221696</v>
       </c>
       <c r="B46" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>137221699</v>
       </c>
       <c r="B47" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>137222847</v>
       </c>
       <c r="B48" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137222849</v>
       </c>
       <c r="B49" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>137222854</v>
       </c>
       <c r="B50" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>137222855</v>
       </c>
       <c r="B51" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>137221687</v>
       </c>
       <c r="B52" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>137222845</v>
       </c>
       <c r="B71" t="n">
-        <v>99399</v>
+        <v>99412</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>137222858</v>
       </c>
       <c r="B72" t="n">
-        <v>99399</v>
+        <v>99412</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>137221672</v>
       </c>
       <c r="B103" t="n">
-        <v>87564</v>
+        <v>87577</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>137221679</v>
       </c>
       <c r="B104" t="n">
-        <v>87564</v>
+        <v>87577</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>137221681</v>
       </c>
       <c r="B105" t="n">
-        <v>87564</v>
+        <v>87577</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>137222848</v>
       </c>
       <c r="B106" t="n">
-        <v>87564</v>
+        <v>87577</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>137221675</v>
       </c>
       <c r="B107" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>137221678</v>
       </c>
       <c r="B108" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>137221680</v>
       </c>
       <c r="B109" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>137221684</v>
       </c>
       <c r="B110" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>137221688</v>
       </c>
       <c r="B111" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>137221854</v>
       </c>
       <c r="B112" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>137221856</v>
       </c>
       <c r="B113" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>137221667</v>
       </c>
       <c r="B114" t="n">
-        <v>87420</v>
+        <v>87433</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>137221677</v>
       </c>
       <c r="B122" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>137221682</v>
       </c>
       <c r="B123" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>137221689</v>
       </c>
       <c r="B124" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>137221697</v>
       </c>
       <c r="B125" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>137221855</v>
       </c>
       <c r="B126" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>137221867</v>
       </c>
       <c r="B127" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>137221880</v>
       </c>
       <c r="B128" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>137221881</v>
       </c>
       <c r="B129" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>137222842</v>
       </c>
       <c r="B130" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>137222856</v>
       </c>
       <c r="B131" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>137221685</v>
       </c>
       <c r="B132" t="n">
-        <v>93451</v>
+        <v>93464</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>137221692</v>
       </c>
       <c r="B133" t="n">
-        <v>93451</v>
+        <v>93464</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>137221698</v>
       </c>
       <c r="B134" t="n">
-        <v>93451</v>
+        <v>93464</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>137221691</v>
       </c>
       <c r="B135" t="n">
-        <v>93456</v>
+        <v>93469</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137221693</v>
       </c>
       <c r="B3" t="n">
-        <v>87401</v>
+        <v>87403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>137221872</v>
       </c>
       <c r="B6" t="n">
-        <v>87576</v>
+        <v>87578</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>137221873</v>
       </c>
       <c r="B8" t="n">
-        <v>90854</v>
+        <v>90856</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>137222914</v>
       </c>
       <c r="B9" t="n">
-        <v>90854</v>
+        <v>90856</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>137221700</v>
       </c>
       <c r="B14" t="n">
-        <v>91576</v>
+        <v>91578</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>137221671</v>
       </c>
       <c r="B15" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>137221853</v>
       </c>
       <c r="B16" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>137221857</v>
       </c>
       <c r="B17" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>137221874</v>
       </c>
       <c r="B18" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>137222844</v>
       </c>
       <c r="B19" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>137222846</v>
       </c>
       <c r="B20" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>137222850</v>
       </c>
       <c r="B21" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>137222857</v>
       </c>
       <c r="B22" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>137222908</v>
       </c>
       <c r="B23" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>137222909</v>
       </c>
       <c r="B24" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>137222912</v>
       </c>
       <c r="B25" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137221668</v>
       </c>
       <c r="B28" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>137221673</v>
       </c>
       <c r="B31" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>137221694</v>
       </c>
       <c r="B32" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>137221869</v>
       </c>
       <c r="B33" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>137221674</v>
       </c>
       <c r="B36" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>137221859</v>
       </c>
       <c r="B37" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>137221864</v>
       </c>
       <c r="B38" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>137221868</v>
       </c>
       <c r="B39" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>137222910</v>
       </c>
       <c r="B40" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>137221669</v>
       </c>
       <c r="B43" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>137221670</v>
       </c>
       <c r="B44" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>137221676</v>
       </c>
       <c r="B45" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>137221696</v>
       </c>
       <c r="B46" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>137221699</v>
       </c>
       <c r="B47" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>137222847</v>
       </c>
       <c r="B48" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137222849</v>
       </c>
       <c r="B49" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>137222854</v>
       </c>
       <c r="B50" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>137222855</v>
       </c>
       <c r="B51" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>137221687</v>
       </c>
       <c r="B52" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>137222845</v>
       </c>
       <c r="B71" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>137222858</v>
       </c>
       <c r="B72" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>137221672</v>
       </c>
       <c r="B103" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>137221679</v>
       </c>
       <c r="B104" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>137221681</v>
       </c>
       <c r="B105" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>137222848</v>
       </c>
       <c r="B106" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>137221675</v>
       </c>
       <c r="B107" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>137221678</v>
       </c>
       <c r="B108" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>137221680</v>
       </c>
       <c r="B109" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>137221684</v>
       </c>
       <c r="B110" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>137221688</v>
       </c>
       <c r="B111" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>137221854</v>
       </c>
       <c r="B112" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>137221856</v>
       </c>
       <c r="B113" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>137221667</v>
       </c>
       <c r="B114" t="n">
-        <v>87433</v>
+        <v>87435</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>137221677</v>
       </c>
       <c r="B122" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>137221682</v>
       </c>
       <c r="B123" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>137221689</v>
       </c>
       <c r="B124" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>137221697</v>
       </c>
       <c r="B125" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>137221855</v>
       </c>
       <c r="B126" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>137221867</v>
       </c>
       <c r="B127" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>137221880</v>
       </c>
       <c r="B128" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>137221881</v>
       </c>
       <c r="B129" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>137222842</v>
       </c>
       <c r="B130" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>137222856</v>
       </c>
       <c r="B131" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>137221685</v>
       </c>
       <c r="B132" t="n">
-        <v>93464</v>
+        <v>93465</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>137221692</v>
       </c>
       <c r="B133" t="n">
-        <v>93464</v>
+        <v>93465</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>137221698</v>
       </c>
       <c r="B134" t="n">
-        <v>93464</v>
+        <v>93465</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>137221691</v>
       </c>
       <c r="B135" t="n">
-        <v>93469</v>
+        <v>93470</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137221693</v>
       </c>
       <c r="B3" t="n">
-        <v>87403</v>
+        <v>87406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>137221872</v>
       </c>
       <c r="B6" t="n">
-        <v>87578</v>
+        <v>87581</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>137221873</v>
       </c>
       <c r="B8" t="n">
-        <v>90856</v>
+        <v>90859</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>137222914</v>
       </c>
       <c r="B9" t="n">
-        <v>90856</v>
+        <v>90859</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>137221700</v>
       </c>
       <c r="B14" t="n">
-        <v>91578</v>
+        <v>91581</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>137221671</v>
       </c>
       <c r="B15" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>137221853</v>
       </c>
       <c r="B16" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>137221857</v>
       </c>
       <c r="B17" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>137221874</v>
       </c>
       <c r="B18" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>137222844</v>
       </c>
       <c r="B19" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>137222846</v>
       </c>
       <c r="B20" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>137222850</v>
       </c>
       <c r="B21" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>137222857</v>
       </c>
       <c r="B22" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>137222908</v>
       </c>
       <c r="B23" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>137222909</v>
       </c>
       <c r="B24" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>137222912</v>
       </c>
       <c r="B25" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137221668</v>
       </c>
       <c r="B28" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>137221673</v>
       </c>
       <c r="B31" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>137221694</v>
       </c>
       <c r="B32" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>137221869</v>
       </c>
       <c r="B33" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>137221674</v>
       </c>
       <c r="B36" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>137221859</v>
       </c>
       <c r="B37" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>137221864</v>
       </c>
       <c r="B38" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>137221868</v>
       </c>
       <c r="B39" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>137222910</v>
       </c>
       <c r="B40" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>137221669</v>
       </c>
       <c r="B43" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>137221670</v>
       </c>
       <c r="B44" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>137221676</v>
       </c>
       <c r="B45" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>137221696</v>
       </c>
       <c r="B46" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>137221699</v>
       </c>
       <c r="B47" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>137222847</v>
       </c>
       <c r="B48" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137222849</v>
       </c>
       <c r="B49" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>137222854</v>
       </c>
       <c r="B50" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>137222855</v>
       </c>
       <c r="B51" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>137222845</v>
       </c>
       <c r="B71" t="n">
-        <v>99414</v>
+        <v>99417</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>137222858</v>
       </c>
       <c r="B72" t="n">
-        <v>99414</v>
+        <v>99417</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>137221672</v>
       </c>
       <c r="B103" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>137221679</v>
       </c>
       <c r="B104" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>137221681</v>
       </c>
       <c r="B105" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>137222848</v>
       </c>
       <c r="B106" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>137221675</v>
       </c>
       <c r="B107" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>137221678</v>
       </c>
       <c r="B108" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>137221680</v>
       </c>
       <c r="B109" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>137221684</v>
       </c>
       <c r="B110" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>137221688</v>
       </c>
       <c r="B111" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>137221854</v>
       </c>
       <c r="B112" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>137221856</v>
       </c>
       <c r="B113" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>137221667</v>
       </c>
       <c r="B114" t="n">
-        <v>87435</v>
+        <v>87438</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>137221677</v>
       </c>
       <c r="B122" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>137221682</v>
       </c>
       <c r="B123" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>137221689</v>
       </c>
       <c r="B124" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>137221697</v>
       </c>
       <c r="B125" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>137221855</v>
       </c>
       <c r="B126" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>137221867</v>
       </c>
       <c r="B127" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>137221880</v>
       </c>
       <c r="B128" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>137221881</v>
       </c>
       <c r="B129" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>137222842</v>
       </c>
       <c r="B130" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>137222856</v>
       </c>
       <c r="B131" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>137221685</v>
       </c>
       <c r="B132" t="n">
-        <v>93465</v>
+        <v>93468</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>137221692</v>
       </c>
       <c r="B133" t="n">
-        <v>93465</v>
+        <v>93468</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>137221698</v>
       </c>
       <c r="B134" t="n">
-        <v>93465</v>
+        <v>93468</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>137221691</v>
       </c>
       <c r="B135" t="n">
-        <v>93470</v>
+        <v>93473</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137221693</v>
       </c>
       <c r="B3" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>137221872</v>
       </c>
       <c r="B6" t="n">
-        <v>87581</v>
+        <v>87591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>137221873</v>
       </c>
       <c r="B8" t="n">
-        <v>90859</v>
+        <v>90869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>137222914</v>
       </c>
       <c r="B9" t="n">
-        <v>90859</v>
+        <v>90869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>137221700</v>
       </c>
       <c r="B14" t="n">
-        <v>91581</v>
+        <v>91591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>137221671</v>
       </c>
       <c r="B15" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>137221853</v>
       </c>
       <c r="B16" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>137221857</v>
       </c>
       <c r="B17" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>137221874</v>
       </c>
       <c r="B18" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>137222844</v>
       </c>
       <c r="B19" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>137222846</v>
       </c>
       <c r="B20" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>137222850</v>
       </c>
       <c r="B21" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>137222857</v>
       </c>
       <c r="B22" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>137222908</v>
       </c>
       <c r="B23" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>137222909</v>
       </c>
       <c r="B24" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>137222912</v>
       </c>
       <c r="B25" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137221668</v>
       </c>
       <c r="B28" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>137221673</v>
       </c>
       <c r="B31" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>137221694</v>
       </c>
       <c r="B32" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>137221869</v>
       </c>
       <c r="B33" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>137221674</v>
       </c>
       <c r="B36" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>137221859</v>
       </c>
       <c r="B37" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>137221864</v>
       </c>
       <c r="B38" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>137221868</v>
       </c>
       <c r="B39" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>137222910</v>
       </c>
       <c r="B40" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>137221669</v>
       </c>
       <c r="B43" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>137221670</v>
       </c>
       <c r="B44" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>137221676</v>
       </c>
       <c r="B45" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>137221696</v>
       </c>
       <c r="B46" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>137221699</v>
       </c>
       <c r="B47" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>137222847</v>
       </c>
       <c r="B48" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137222849</v>
       </c>
       <c r="B49" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>137222854</v>
       </c>
       <c r="B50" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>137222855</v>
       </c>
       <c r="B51" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>137221687</v>
       </c>
       <c r="B52" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>137222845</v>
       </c>
       <c r="B71" t="n">
-        <v>99417</v>
+        <v>99427</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>137222858</v>
       </c>
       <c r="B72" t="n">
-        <v>99417</v>
+        <v>99427</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>137221672</v>
       </c>
       <c r="B103" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>137221679</v>
       </c>
       <c r="B104" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>137221681</v>
       </c>
       <c r="B105" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>137222848</v>
       </c>
       <c r="B106" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>137221675</v>
       </c>
       <c r="B107" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>137221678</v>
       </c>
       <c r="B108" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>137221680</v>
       </c>
       <c r="B109" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>137221684</v>
       </c>
       <c r="B110" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>137221688</v>
       </c>
       <c r="B111" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>137221854</v>
       </c>
       <c r="B112" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>137221856</v>
       </c>
       <c r="B113" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>137221667</v>
       </c>
       <c r="B114" t="n">
-        <v>87438</v>
+        <v>87448</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>137221677</v>
       </c>
       <c r="B122" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>137221682</v>
       </c>
       <c r="B123" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>137221689</v>
       </c>
       <c r="B124" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>137221697</v>
       </c>
       <c r="B125" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>137221855</v>
       </c>
       <c r="B126" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>137221867</v>
       </c>
       <c r="B127" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>137221880</v>
       </c>
       <c r="B128" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>137221881</v>
       </c>
       <c r="B129" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>137222842</v>
       </c>
       <c r="B130" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>137222856</v>
       </c>
       <c r="B131" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>137221685</v>
       </c>
       <c r="B132" t="n">
-        <v>93468</v>
+        <v>93478</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>137221692</v>
       </c>
       <c r="B133" t="n">
-        <v>93468</v>
+        <v>93478</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>137221698</v>
       </c>
       <c r="B134" t="n">
-        <v>93468</v>
+        <v>93478</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>137221691</v>
       </c>
       <c r="B135" t="n">
-        <v>93473</v>
+        <v>93483</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137221693</v>
       </c>
       <c r="B3" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>137221872</v>
       </c>
       <c r="B6" t="n">
-        <v>87591</v>
+        <v>87592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>137221873</v>
       </c>
       <c r="B8" t="n">
-        <v>90869</v>
+        <v>90870</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>137222914</v>
       </c>
       <c r="B9" t="n">
-        <v>90869</v>
+        <v>90870</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>137221700</v>
       </c>
       <c r="B14" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>137221671</v>
       </c>
       <c r="B15" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>137221853</v>
       </c>
       <c r="B16" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>137221857</v>
       </c>
       <c r="B17" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>137221874</v>
       </c>
       <c r="B18" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>137222844</v>
       </c>
       <c r="B19" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>137222846</v>
       </c>
       <c r="B20" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>137222850</v>
       </c>
       <c r="B21" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>137222857</v>
       </c>
       <c r="B22" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>137222908</v>
       </c>
       <c r="B23" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>137222909</v>
       </c>
       <c r="B24" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>137222912</v>
       </c>
       <c r="B25" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137221668</v>
       </c>
       <c r="B28" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>137221673</v>
       </c>
       <c r="B31" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>137221694</v>
       </c>
       <c r="B32" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>137221869</v>
       </c>
       <c r="B33" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>137221674</v>
       </c>
       <c r="B36" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>137221859</v>
       </c>
       <c r="B37" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>137221864</v>
       </c>
       <c r="B38" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>137221868</v>
       </c>
       <c r="B39" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>137222910</v>
       </c>
       <c r="B40" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>137221669</v>
       </c>
       <c r="B43" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>137221670</v>
       </c>
       <c r="B44" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>137221676</v>
       </c>
       <c r="B45" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>137221696</v>
       </c>
       <c r="B46" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>137221699</v>
       </c>
       <c r="B47" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>137222847</v>
       </c>
       <c r="B48" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137222849</v>
       </c>
       <c r="B49" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>137222854</v>
       </c>
       <c r="B50" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>137222855</v>
       </c>
       <c r="B51" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>137222845</v>
       </c>
       <c r="B71" t="n">
-        <v>99427</v>
+        <v>99428</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>137222858</v>
       </c>
       <c r="B72" t="n">
-        <v>99427</v>
+        <v>99428</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>137221672</v>
       </c>
       <c r="B103" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>137221679</v>
       </c>
       <c r="B104" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>137221681</v>
       </c>
       <c r="B105" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>137222848</v>
       </c>
       <c r="B106" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>137221675</v>
       </c>
       <c r="B107" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>137221678</v>
       </c>
       <c r="B108" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>137221680</v>
       </c>
       <c r="B109" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>137221684</v>
       </c>
       <c r="B110" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>137221688</v>
       </c>
       <c r="B111" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>137221854</v>
       </c>
       <c r="B112" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>137221856</v>
       </c>
       <c r="B113" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>137221667</v>
       </c>
       <c r="B114" t="n">
-        <v>87448</v>
+        <v>87449</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>137221677</v>
       </c>
       <c r="B122" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>137221682</v>
       </c>
       <c r="B123" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>137221689</v>
       </c>
       <c r="B124" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>137221697</v>
       </c>
       <c r="B125" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>137221855</v>
       </c>
       <c r="B126" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>137221867</v>
       </c>
       <c r="B127" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>137221880</v>
       </c>
       <c r="B128" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>137221881</v>
       </c>
       <c r="B129" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>137222842</v>
       </c>
       <c r="B130" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>137222856</v>
       </c>
       <c r="B131" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>137221685</v>
       </c>
       <c r="B132" t="n">
-        <v>93478</v>
+        <v>93479</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>137221692</v>
       </c>
       <c r="B133" t="n">
-        <v>93478</v>
+        <v>93479</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>137221698</v>
       </c>
       <c r="B134" t="n">
-        <v>93478</v>
+        <v>93479</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>137221691</v>
       </c>
       <c r="B135" t="n">
-        <v>93483</v>
+        <v>93484</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137221693</v>
       </c>
       <c r="B3" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>137221872</v>
       </c>
       <c r="B6" t="n">
-        <v>87592</v>
+        <v>87595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>137221873</v>
       </c>
       <c r="B8" t="n">
-        <v>90870</v>
+        <v>90873</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>137222914</v>
       </c>
       <c r="B9" t="n">
-        <v>90870</v>
+        <v>90873</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>137221700</v>
       </c>
       <c r="B14" t="n">
-        <v>91592</v>
+        <v>91595</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>137221671</v>
       </c>
       <c r="B15" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>137221853</v>
       </c>
       <c r="B16" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>137221857</v>
       </c>
       <c r="B17" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>137221874</v>
       </c>
       <c r="B18" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>137222844</v>
       </c>
       <c r="B19" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>137222846</v>
       </c>
       <c r="B20" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>137222850</v>
       </c>
       <c r="B21" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>137222857</v>
       </c>
       <c r="B22" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>137222908</v>
       </c>
       <c r="B23" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>137222909</v>
       </c>
       <c r="B24" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>137222912</v>
       </c>
       <c r="B25" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137221668</v>
       </c>
       <c r="B28" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>137221673</v>
       </c>
       <c r="B31" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>137221694</v>
       </c>
       <c r="B32" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>137221869</v>
       </c>
       <c r="B33" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>137221674</v>
       </c>
       <c r="B36" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>137221859</v>
       </c>
       <c r="B37" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>137221864</v>
       </c>
       <c r="B38" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>137221868</v>
       </c>
       <c r="B39" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>137222910</v>
       </c>
       <c r="B40" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>137221669</v>
       </c>
       <c r="B43" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>137221670</v>
       </c>
       <c r="B44" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>137221676</v>
       </c>
       <c r="B45" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>137221696</v>
       </c>
       <c r="B46" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>137221699</v>
       </c>
       <c r="B47" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>137222847</v>
       </c>
       <c r="B48" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137222849</v>
       </c>
       <c r="B49" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>137222854</v>
       </c>
       <c r="B50" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>137222855</v>
       </c>
       <c r="B51" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>137221687</v>
       </c>
       <c r="B52" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>137222845</v>
       </c>
       <c r="B71" t="n">
-        <v>99428</v>
+        <v>99433</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>137222858</v>
       </c>
       <c r="B72" t="n">
-        <v>99428</v>
+        <v>99433</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>137221672</v>
       </c>
       <c r="B103" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>137221679</v>
       </c>
       <c r="B104" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>137221681</v>
       </c>
       <c r="B105" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>137222848</v>
       </c>
       <c r="B106" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>137221675</v>
       </c>
       <c r="B107" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>137221678</v>
       </c>
       <c r="B108" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>137221680</v>
       </c>
       <c r="B109" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>137221684</v>
       </c>
       <c r="B110" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>137221688</v>
       </c>
       <c r="B111" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>137221854</v>
       </c>
       <c r="B112" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>137221856</v>
       </c>
       <c r="B113" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>137221667</v>
       </c>
       <c r="B114" t="n">
-        <v>87449</v>
+        <v>87452</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>137221677</v>
       </c>
       <c r="B122" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>137221682</v>
       </c>
       <c r="B123" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>137221689</v>
       </c>
       <c r="B124" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>137221697</v>
       </c>
       <c r="B125" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>137221855</v>
       </c>
       <c r="B126" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>137221867</v>
       </c>
       <c r="B127" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>137221880</v>
       </c>
       <c r="B128" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>137221881</v>
       </c>
       <c r="B129" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>137222842</v>
       </c>
       <c r="B130" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>137222856</v>
       </c>
       <c r="B131" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>137221685</v>
       </c>
       <c r="B132" t="n">
-        <v>93479</v>
+        <v>93484</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>137221692</v>
       </c>
       <c r="B133" t="n">
-        <v>93479</v>
+        <v>93484</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>137221698</v>
       </c>
       <c r="B134" t="n">
-        <v>93479</v>
+        <v>93484</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>137221691</v>
       </c>
       <c r="B135" t="n">
-        <v>93484</v>
+        <v>93489</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -2000,7 +2000,7 @@
         <v>137221700</v>
       </c>
       <c r="B14" t="n">
-        <v>91595</v>
+        <v>91597</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>137221674</v>
       </c>
       <c r="B36" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>137221859</v>
       </c>
       <c r="B37" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>137221864</v>
       </c>
       <c r="B38" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>137221868</v>
       </c>
       <c r="B39" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>137222910</v>
       </c>
       <c r="B40" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>137221669</v>
       </c>
       <c r="B43" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>137221670</v>
       </c>
       <c r="B44" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>137221676</v>
       </c>
       <c r="B45" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>137221696</v>
       </c>
       <c r="B46" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>137221699</v>
       </c>
       <c r="B47" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>137222847</v>
       </c>
       <c r="B48" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137222849</v>
       </c>
       <c r="B49" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>137222854</v>
       </c>
       <c r="B50" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>137222855</v>
       </c>
       <c r="B51" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>137222845</v>
       </c>
       <c r="B71" t="n">
-        <v>99433</v>
+        <v>99435</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>137222858</v>
       </c>
       <c r="B72" t="n">
-        <v>99433</v>
+        <v>99435</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>137221685</v>
       </c>
       <c r="B132" t="n">
-        <v>93484</v>
+        <v>93486</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>137221692</v>
       </c>
       <c r="B133" t="n">
-        <v>93484</v>
+        <v>93486</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>137221698</v>
       </c>
       <c r="B134" t="n">
-        <v>93484</v>
+        <v>93486</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>137221691</v>
       </c>
       <c r="B135" t="n">
-        <v>93489</v>
+        <v>93491</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137221693</v>
       </c>
       <c r="B3" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>137221872</v>
       </c>
       <c r="B6" t="n">
-        <v>87595</v>
+        <v>87600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>137221873</v>
       </c>
       <c r="B8" t="n">
-        <v>90873</v>
+        <v>90878</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>137222914</v>
       </c>
       <c r="B9" t="n">
-        <v>90873</v>
+        <v>90878</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>137221700</v>
       </c>
       <c r="B14" t="n">
-        <v>91597</v>
+        <v>91602</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>137221671</v>
       </c>
       <c r="B15" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>137221853</v>
       </c>
       <c r="B16" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>137221857</v>
       </c>
       <c r="B17" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>137221874</v>
       </c>
       <c r="B18" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>137222844</v>
       </c>
       <c r="B19" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>137222846</v>
       </c>
       <c r="B20" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>137222850</v>
       </c>
       <c r="B21" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>137222857</v>
       </c>
       <c r="B22" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>137222908</v>
       </c>
       <c r="B23" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>137222909</v>
       </c>
       <c r="B24" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>137222912</v>
       </c>
       <c r="B25" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137221668</v>
       </c>
       <c r="B28" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>137221673</v>
       </c>
       <c r="B31" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>137221694</v>
       </c>
       <c r="B32" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>137221869</v>
       </c>
       <c r="B33" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>137221674</v>
       </c>
       <c r="B36" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>137221859</v>
       </c>
       <c r="B37" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>137221864</v>
       </c>
       <c r="B38" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>137221868</v>
       </c>
       <c r="B39" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>137222910</v>
       </c>
       <c r="B40" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>137221669</v>
       </c>
       <c r="B43" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>137221670</v>
       </c>
       <c r="B44" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>137221676</v>
       </c>
       <c r="B45" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>137221696</v>
       </c>
       <c r="B46" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>137221699</v>
       </c>
       <c r="B47" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>137222847</v>
       </c>
       <c r="B48" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137222849</v>
       </c>
       <c r="B49" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>137222854</v>
       </c>
       <c r="B50" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>137222855</v>
       </c>
       <c r="B51" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>137221687</v>
       </c>
       <c r="B52" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>137222845</v>
       </c>
       <c r="B71" t="n">
-        <v>99435</v>
+        <v>99441</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>137222858</v>
       </c>
       <c r="B72" t="n">
-        <v>99435</v>
+        <v>99441</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>137221672</v>
       </c>
       <c r="B103" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>137221679</v>
       </c>
       <c r="B104" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>137221681</v>
       </c>
       <c r="B105" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>137222848</v>
       </c>
       <c r="B106" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>137221675</v>
       </c>
       <c r="B107" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>137221678</v>
       </c>
       <c r="B108" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>137221680</v>
       </c>
       <c r="B109" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>137221684</v>
       </c>
       <c r="B110" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>137221688</v>
       </c>
       <c r="B111" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>137221854</v>
       </c>
       <c r="B112" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>137221856</v>
       </c>
       <c r="B113" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>137221667</v>
       </c>
       <c r="B114" t="n">
-        <v>87452</v>
+        <v>87457</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>137221677</v>
       </c>
       <c r="B122" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>137221682</v>
       </c>
       <c r="B123" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>137221689</v>
       </c>
       <c r="B124" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>137221697</v>
       </c>
       <c r="B125" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>137221855</v>
       </c>
       <c r="B126" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>137221867</v>
       </c>
       <c r="B127" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>137221880</v>
       </c>
       <c r="B128" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>137221881</v>
       </c>
       <c r="B129" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>137222842</v>
       </c>
       <c r="B130" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>137222856</v>
       </c>
       <c r="B131" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>137221685</v>
       </c>
       <c r="B132" t="n">
-        <v>93486</v>
+        <v>93492</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>137221692</v>
       </c>
       <c r="B133" t="n">
-        <v>93486</v>
+        <v>93492</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>137221698</v>
       </c>
       <c r="B134" t="n">
-        <v>93486</v>
+        <v>93492</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>137221691</v>
       </c>
       <c r="B135" t="n">
-        <v>93491</v>
+        <v>93497</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137221693</v>
       </c>
       <c r="B3" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>137221872</v>
       </c>
       <c r="B6" t="n">
-        <v>87600</v>
+        <v>87611</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>137221873</v>
       </c>
       <c r="B8" t="n">
-        <v>90878</v>
+        <v>90889</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>137222914</v>
       </c>
       <c r="B9" t="n">
-        <v>90878</v>
+        <v>90889</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>137221700</v>
       </c>
       <c r="B14" t="n">
-        <v>91602</v>
+        <v>91614</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>137221671</v>
       </c>
       <c r="B15" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>137221853</v>
       </c>
       <c r="B16" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>137221857</v>
       </c>
       <c r="B17" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>137221874</v>
       </c>
       <c r="B18" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>137222844</v>
       </c>
       <c r="B19" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>137222846</v>
       </c>
       <c r="B20" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>137222850</v>
       </c>
       <c r="B21" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>137222857</v>
       </c>
       <c r="B22" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>137222908</v>
       </c>
       <c r="B23" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>137222909</v>
       </c>
       <c r="B24" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>137222912</v>
       </c>
       <c r="B25" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137221668</v>
       </c>
       <c r="B28" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>137221673</v>
       </c>
       <c r="B31" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>137221694</v>
       </c>
       <c r="B32" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>137221869</v>
       </c>
       <c r="B33" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>137221674</v>
       </c>
       <c r="B36" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>137221859</v>
       </c>
       <c r="B37" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>137221864</v>
       </c>
       <c r="B38" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>137221868</v>
       </c>
       <c r="B39" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>137222910</v>
       </c>
       <c r="B40" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>137221669</v>
       </c>
       <c r="B43" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>137221670</v>
       </c>
       <c r="B44" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>137221676</v>
       </c>
       <c r="B45" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>137221696</v>
       </c>
       <c r="B46" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>137221699</v>
       </c>
       <c r="B47" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>137222847</v>
       </c>
       <c r="B48" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137222849</v>
       </c>
       <c r="B49" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>137222854</v>
       </c>
       <c r="B50" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>137222855</v>
       </c>
       <c r="B51" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>137222845</v>
       </c>
       <c r="B71" t="n">
-        <v>99441</v>
+        <v>99453</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>137222858</v>
       </c>
       <c r="B72" t="n">
-        <v>99441</v>
+        <v>99453</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>137221672</v>
       </c>
       <c r="B103" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>137221679</v>
       </c>
       <c r="B104" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>137221681</v>
       </c>
       <c r="B105" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>137222848</v>
       </c>
       <c r="B106" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>137221675</v>
       </c>
       <c r="B107" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>137221678</v>
       </c>
       <c r="B108" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>137221680</v>
       </c>
       <c r="B109" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>137221684</v>
       </c>
       <c r="B110" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>137221688</v>
       </c>
       <c r="B111" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>137221854</v>
       </c>
       <c r="B112" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>137221856</v>
       </c>
       <c r="B113" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>137221667</v>
       </c>
       <c r="B114" t="n">
-        <v>87457</v>
+        <v>87468</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>137221677</v>
       </c>
       <c r="B122" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>137221682</v>
       </c>
       <c r="B123" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>137221689</v>
       </c>
       <c r="B124" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>137221697</v>
       </c>
       <c r="B125" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>137221855</v>
       </c>
       <c r="B126" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>137221867</v>
       </c>
       <c r="B127" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>137221880</v>
       </c>
       <c r="B128" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>137221881</v>
       </c>
       <c r="B129" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>137222842</v>
       </c>
       <c r="B130" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>137222856</v>
       </c>
       <c r="B131" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>137221685</v>
       </c>
       <c r="B132" t="n">
-        <v>93492</v>
+        <v>93504</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>137221692</v>
       </c>
       <c r="B133" t="n">
-        <v>93492</v>
+        <v>93504</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>137221698</v>
       </c>
       <c r="B134" t="n">
-        <v>93492</v>
+        <v>93504</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>137221691</v>
       </c>
       <c r="B135" t="n">
-        <v>93497</v>
+        <v>93509</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137221693</v>
       </c>
       <c r="B3" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>137221872</v>
       </c>
       <c r="B6" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>137221873</v>
       </c>
       <c r="B8" t="n">
-        <v>90889</v>
+        <v>90890</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>137222914</v>
       </c>
       <c r="B9" t="n">
-        <v>90889</v>
+        <v>90890</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>137221700</v>
       </c>
       <c r="B14" t="n">
-        <v>91614</v>
+        <v>91615</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>137221671</v>
       </c>
       <c r="B15" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>137221853</v>
       </c>
       <c r="B16" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>137221857</v>
       </c>
       <c r="B17" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>137221874</v>
       </c>
       <c r="B18" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>137222844</v>
       </c>
       <c r="B19" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>137222846</v>
       </c>
       <c r="B20" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>137222850</v>
       </c>
       <c r="B21" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>137222857</v>
       </c>
       <c r="B22" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>137222908</v>
       </c>
       <c r="B23" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>137222909</v>
       </c>
       <c r="B24" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>137222912</v>
       </c>
       <c r="B25" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137221668</v>
       </c>
       <c r="B28" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>137221673</v>
       </c>
       <c r="B31" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>137221694</v>
       </c>
       <c r="B32" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>137221869</v>
       </c>
       <c r="B33" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>137221674</v>
       </c>
       <c r="B36" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>137221859</v>
       </c>
       <c r="B37" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>137221864</v>
       </c>
       <c r="B38" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>137221868</v>
       </c>
       <c r="B39" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>137222910</v>
       </c>
       <c r="B40" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>137221669</v>
       </c>
       <c r="B43" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>137221670</v>
       </c>
       <c r="B44" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>137221676</v>
       </c>
       <c r="B45" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>137221696</v>
       </c>
       <c r="B46" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>137221699</v>
       </c>
       <c r="B47" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>137222847</v>
       </c>
       <c r="B48" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137222849</v>
       </c>
       <c r="B49" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>137222854</v>
       </c>
       <c r="B50" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>137222855</v>
       </c>
       <c r="B51" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>137222845</v>
       </c>
       <c r="B71" t="n">
-        <v>99453</v>
+        <v>99454</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>137222858</v>
       </c>
       <c r="B72" t="n">
-        <v>99453</v>
+        <v>99454</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>137221672</v>
       </c>
       <c r="B103" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>137221679</v>
       </c>
       <c r="B104" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>137221681</v>
       </c>
       <c r="B105" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>137222848</v>
       </c>
       <c r="B106" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>137221675</v>
       </c>
       <c r="B107" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>137221678</v>
       </c>
       <c r="B108" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>137221680</v>
       </c>
       <c r="B109" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>137221684</v>
       </c>
       <c r="B110" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>137221688</v>
       </c>
       <c r="B111" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>137221854</v>
       </c>
       <c r="B112" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>137221856</v>
       </c>
       <c r="B113" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>137221667</v>
       </c>
       <c r="B114" t="n">
-        <v>87468</v>
+        <v>87469</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>137221677</v>
       </c>
       <c r="B122" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>137221682</v>
       </c>
       <c r="B123" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>137221689</v>
       </c>
       <c r="B124" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>137221697</v>
       </c>
       <c r="B125" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>137221855</v>
       </c>
       <c r="B126" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>137221867</v>
       </c>
       <c r="B127" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>137221880</v>
       </c>
       <c r="B128" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>137221881</v>
       </c>
       <c r="B129" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>137222842</v>
       </c>
       <c r="B130" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>137222856</v>
       </c>
       <c r="B131" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>137221685</v>
       </c>
       <c r="B132" t="n">
-        <v>93504</v>
+        <v>93505</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>137221692</v>
       </c>
       <c r="B133" t="n">
-        <v>93504</v>
+        <v>93505</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>137221698</v>
       </c>
       <c r="B134" t="n">
-        <v>93504</v>
+        <v>93505</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>137221691</v>
       </c>
       <c r="B135" t="n">
-        <v>93509</v>
+        <v>93510</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137221693</v>
       </c>
       <c r="B3" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>137221872</v>
       </c>
       <c r="B6" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>137221873</v>
       </c>
       <c r="B8" t="n">
-        <v>90890</v>
+        <v>90893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>137222914</v>
       </c>
       <c r="B9" t="n">
-        <v>90890</v>
+        <v>90893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>137221700</v>
       </c>
       <c r="B14" t="n">
-        <v>91615</v>
+        <v>91618</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>137221671</v>
       </c>
       <c r="B15" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>137221853</v>
       </c>
       <c r="B16" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>137221857</v>
       </c>
       <c r="B17" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>137221874</v>
       </c>
       <c r="B18" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>137222844</v>
       </c>
       <c r="B19" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>137222846</v>
       </c>
       <c r="B20" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>137222850</v>
       </c>
       <c r="B21" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>137222857</v>
       </c>
       <c r="B22" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>137222908</v>
       </c>
       <c r="B23" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>137222909</v>
       </c>
       <c r="B24" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>137222912</v>
       </c>
       <c r="B25" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137221668</v>
       </c>
       <c r="B28" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>137221673</v>
       </c>
       <c r="B31" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>137221694</v>
       </c>
       <c r="B32" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>137221869</v>
       </c>
       <c r="B33" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>137221674</v>
       </c>
       <c r="B36" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>137221859</v>
       </c>
       <c r="B37" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>137221864</v>
       </c>
       <c r="B38" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>137221868</v>
       </c>
       <c r="B39" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>137222910</v>
       </c>
       <c r="B40" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>137221669</v>
       </c>
       <c r="B43" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>137221670</v>
       </c>
       <c r="B44" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>137221676</v>
       </c>
       <c r="B45" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>137221696</v>
       </c>
       <c r="B46" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>137221699</v>
       </c>
       <c r="B47" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>137222847</v>
       </c>
       <c r="B48" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137222849</v>
       </c>
       <c r="B49" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>137222854</v>
       </c>
       <c r="B50" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>137222855</v>
       </c>
       <c r="B51" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>137222845</v>
       </c>
       <c r="B71" t="n">
-        <v>99454</v>
+        <v>99457</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>137222858</v>
       </c>
       <c r="B72" t="n">
-        <v>99454</v>
+        <v>99457</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>137221672</v>
       </c>
       <c r="B103" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>137221679</v>
       </c>
       <c r="B104" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>137221681</v>
       </c>
       <c r="B105" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>137222848</v>
       </c>
       <c r="B106" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>137221675</v>
       </c>
       <c r="B107" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>137221678</v>
       </c>
       <c r="B108" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>137221680</v>
       </c>
       <c r="B109" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>137221684</v>
       </c>
       <c r="B110" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>137221688</v>
       </c>
       <c r="B111" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>137221854</v>
       </c>
       <c r="B112" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>137221856</v>
       </c>
       <c r="B113" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>137221667</v>
       </c>
       <c r="B114" t="n">
-        <v>87469</v>
+        <v>87472</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>137221677</v>
       </c>
       <c r="B122" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>137221682</v>
       </c>
       <c r="B123" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>137221689</v>
       </c>
       <c r="B124" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>137221697</v>
       </c>
       <c r="B125" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>137221855</v>
       </c>
       <c r="B126" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>137221867</v>
       </c>
       <c r="B127" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>137221880</v>
       </c>
       <c r="B128" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>137221881</v>
       </c>
       <c r="B129" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>137222842</v>
       </c>
       <c r="B130" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>137222856</v>
       </c>
       <c r="B131" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>137221685</v>
       </c>
       <c r="B132" t="n">
-        <v>93505</v>
+        <v>93508</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>137221692</v>
       </c>
       <c r="B133" t="n">
-        <v>93505</v>
+        <v>93508</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>137221698</v>
       </c>
       <c r="B134" t="n">
-        <v>93505</v>
+        <v>93508</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>137221691</v>
       </c>
       <c r="B135" t="n">
-        <v>93510</v>
+        <v>93513</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 530-2024 artfynd.xlsx
+++ b/artfynd/A 530-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>137221693</v>
       </c>
       <c r="B3" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>137221872</v>
       </c>
       <c r="B6" t="n">
-        <v>87615</v>
+        <v>87619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>137221873</v>
       </c>
       <c r="B8" t="n">
-        <v>90893</v>
+        <v>90897</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>137222914</v>
       </c>
       <c r="B9" t="n">
-        <v>90893</v>
+        <v>90897</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>137221700</v>
       </c>
       <c r="B14" t="n">
-        <v>91618</v>
+        <v>91622</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>137221671</v>
       </c>
       <c r="B15" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>137221853</v>
       </c>
       <c r="B16" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>137221857</v>
       </c>
       <c r="B17" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>137221874</v>
       </c>
       <c r="B18" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>137222844</v>
       </c>
       <c r="B19" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>137222846</v>
       </c>
       <c r="B20" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>137222850</v>
       </c>
       <c r="B21" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>137222857</v>
       </c>
       <c r="B22" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>137222908</v>
       </c>
       <c r="B23" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>137222909</v>
       </c>
       <c r="B24" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>137222912</v>
       </c>
       <c r="B25" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137221668</v>
       </c>
       <c r="B28" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>137221673</v>
       </c>
       <c r="B31" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>137221694</v>
       </c>
       <c r="B32" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>137221869</v>
       </c>
       <c r="B33" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>137221674</v>
       </c>
       <c r="B36" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>137221859</v>
       </c>
       <c r="B37" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>137221864</v>
       </c>
       <c r="B38" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>137221868</v>
       </c>
       <c r="B39" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>137222910</v>
       </c>
       <c r="B40" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>137221669</v>
       </c>
       <c r="B43" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>137221670</v>
       </c>
       <c r="B44" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>137221676</v>
       </c>
       <c r="B45" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>137221696</v>
       </c>
       <c r="B46" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>137221699</v>
       </c>
       <c r="B47" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         <v>137222847</v>
       </c>
       <c r="B48" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>137222849</v>
       </c>
       <c r="B49" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>137222854</v>
       </c>
       <c r="B50" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>137222855</v>
       </c>
       <c r="B51" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         <v>137221687</v>
       </c>
       <c r="B52" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>137222845</v>
       </c>
       <c r="B71" t="n">
-        <v>99457</v>
+        <v>99461</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>137222858</v>
       </c>
       <c r="B72" t="n">
-        <v>99457</v>
+        <v>99461</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>137221672</v>
       </c>
       <c r="B103" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>137221679</v>
       </c>
       <c r="B104" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>137221681</v>
       </c>
       <c r="B105" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>137222848</v>
       </c>
       <c r="B106" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>137221675</v>
       </c>
       <c r="B107" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>137221678</v>
       </c>
       <c r="B108" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>137221680</v>
       </c>
       <c r="B109" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
         <v>137221684</v>
       </c>
       <c r="B110" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>137221688</v>
       </c>
       <c r="B111" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>137221854</v>
       </c>
       <c r="B112" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>137221856</v>
       </c>
       <c r="B113" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>137221667</v>
       </c>
       <c r="B114" t="n">
-        <v>87472</v>
+        <v>87476</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>137221677</v>
       </c>
       <c r="B122" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>137221682</v>
       </c>
       <c r="B123" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>137221689</v>
       </c>
       <c r="B124" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>137221697</v>
       </c>
       <c r="B125" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>137221855</v>
       </c>
       <c r="B126" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>137221867</v>
       </c>
       <c r="B127" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>137221880</v>
       </c>
       <c r="B128" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>137221881</v>
       </c>
       <c r="B129" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>137222842</v>
       </c>
       <c r="B130" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>137222856</v>
       </c>
       <c r="B131" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>137221685</v>
       </c>
       <c r="B132" t="n">
-        <v>93508</v>
+        <v>93512</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>137221692</v>
       </c>
       <c r="B133" t="n">
-        <v>93508</v>
+        <v>93512</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>137221698</v>
       </c>
       <c r="B134" t="n">
-        <v>93508</v>
+        <v>93512</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>137221691</v>
       </c>
       <c r="B135" t="n">
-        <v>93513</v>
+        <v>93517</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
